--- a/data/HR1/Shared ESS/HR1_ESS.xlsx
+++ b/data/HR1/Shared ESS/HR1_ESS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\HR1\Shared ESS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Shared ESS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EA081C-AB64-481B-8B63-2F800633C8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ED936D-F119-451E-A679-B6E072B7D176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31920" yWindow="-11265" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="81" r:id="rId1"/>
@@ -494,13 +494,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="1">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D1" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="E1" s="1">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -510,22 +510,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7614B8E9-E001-4C19-AEEE-8FBC4B48A529}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="4">
+        <f>C2</f>
+        <v>1.0819000000000001</v>
+      </c>
+      <c r="C2">
         <v>1.0819000000000001</v>
       </c>
     </row>
